--- a/WorkBot/main/data/orders/Sysco/Sysco_Bakery_20260707.xlsx
+++ b/WorkBot/main/data/orders/Sysco/Sysco_Bakery_20260707.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,6 +542,552 @@
         <v>16.17</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5833462</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jalapenos (Sliced)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>54.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4684250</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Shortening - All Purpose (Palm)</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="E10" t="n">
+        <v>71.75</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5268382</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dirty Chip - Cracked Pepper (2oz)</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>20.08</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5241070</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dirty Chip - Sour Cream &amp; Onion (2oz)</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="E12" t="n">
+        <v>20.08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5210646</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dirty Chip - Salt &amp; Vinegar (2oz)</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="E13" t="n">
+        <v>20.05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>5350725</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dirty Chip - Sea Salted (2oz)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="E14" t="n">
+        <v>61.89</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0017354</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hash Brown</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="E15" t="n">
+        <v>46.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>7456025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Egg Patty - Whites</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="E16" t="n">
+        <v>37.13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1589290</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sausage - Patty (Retail)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>24.51</v>
+      </c>
+      <c r="E17" t="n">
+        <v>73.53</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1024421</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FRZ Fruit - Strawberry (Whole)</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>48</v>
+      </c>
+      <c r="E18" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3837541</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Danish - Mini Assorted (Signature)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>60.84</v>
+      </c>
+      <c r="E19" t="n">
+        <v>60.84</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>7338945</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Cold Foam - Whipped Cream</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>53.99</v>
+      </c>
+      <c r="E20" t="n">
+        <v>53.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4136768</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PKT Ketchup</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>40.03</v>
+      </c>
+      <c r="E21" t="n">
+        <v>40.03</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2673867</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PKT Mayo</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="E22" t="n">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8337503</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Avocado - Hand Scooped</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="E23" t="n">
+        <v>227.96</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>7226918</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Mozz (Sliced)</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="E24" t="n">
+        <v>83.67</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>9035601</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>American Cheese (Sliced)</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="E25" t="n">
+        <v>45.01</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6297594</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Avocado - Halves Fresh</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>32.69</v>
+      </c>
+      <c r="E26" t="n">
+        <v>32.69</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7128077</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Olive - Kalamata (Pitted)</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>60.59</v>
+      </c>
+      <c r="E27" t="n">
+        <v>242.36</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2366607</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Liquid Egg</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>49.03</v>
+      </c>
+      <c r="E28" t="n">
+        <v>245.15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1101324</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ricotta - Impastata</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="E29" t="n">
+        <v>56.98</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4828802</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Heavy Cream</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>47.41</v>
+      </c>
+      <c r="E30" t="n">
+        <v>142.23</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3716743</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Philadelphia Cream Cheese - Original</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>109.77</v>
+      </c>
+      <c r="E31" t="n">
+        <v>219.54</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1161181</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cream Cheese</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>15</v>
+      </c>
+      <c r="D32" t="n">
+        <v>53.24</v>
+      </c>
+      <c r="E32" t="n">
+        <v>798.6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>7233411</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Muffin Batter - Choc Chip</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>72.06</v>
+      </c>
+      <c r="E33" t="n">
+        <v>216.18</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1681535</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Muffin Batter - Blueberry</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="E34" t="n">
+        <v>110.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
